--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/big_sister.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/big_sister.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Tem alguém aí?</t>
+          <t>Tem, tem alguém aí?</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Veja, #bigdaddy, um anjo... Veja... Um anjo!</t>
+          <t>Olha, #bigdaddy, um anjo... vê... um anjo!</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>... Hehe, minha imaginação está meio estranha de novo. Sinto muito, #bigdaddy... Mas, se um anjo realmente viesse até nós... Que maravilha seria.</t>
+          <t>...Hehe, minha cabeça está engraçada de novo. Desculpa, #bigdaddy...Mas, se um anjo de verdade veio até nós... que maravilha seria.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Temos que proteger os Pequenos, não é, #bigdaddy, certo...? O mundo lá fora é tão... assustador. Só o Pequeno Jardim é seguro, nosso... lar.</t>
+          <t>Temos de proteger os Pequeninos, né, #bigdaddy, né...? O mundo lá fora é tão... assustador. Só o Pequeno Jardim é seguro, o nosso... lar.</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>... Sim, é nossa missão. Proteger os Pequenos. Esse é nosso... Dever, #bigdaddy? Não vamos perdoar ninguém que machuque os Pequenos.</t>
+          <t>...Sim, é a nossa missão. Proteger os Pequeninos. Essa é a nossa... né, #bigdaddy? Não perdoaremos ninguém que machucar os Pequeninos.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Pobrezinhos... Os Pequenos estão perdidos no mundo lá fora. Eles não conhecem nosso Pequeno Jardim. Estão perdidos, #bigdaddy.</t>
+          <t>Coitados...os Pequeninos estão perdidos no mundo lá fora. Eles não conhecem o nosso Pequeno Jardim. Estão perdidos, #bigdaddy.</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>... Hehe, se realmente existissem anjos, seria tão maravilhoso. Os anjos com certeza viriam nos ajudar... porque é isso que os anjos fazem. Eles encontrariam os Pequenos e os trariam pra cá. Ei, #bigdaddy, os anjos com certeza virão nos ajudar.</t>
+          <t>...Hehe, se realmente houvesse anjos, que maravilha seria. Os anjos certamente viriam nos ajudar... porque é isso que anjos fazem. Eles achariam os Pequeninos e os trariam para cá. Ei, #bigdaddy, os anjos certamente virão nos ajudar.</t>
         </is>
       </c>
     </row>
@@ -697,8 +697,8 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>... Hehe, uma nova Pequena chegou até nós, #bigdaddy. Não está mais perdida. A partir de agora, vamos protegê-la, custe o que custar... Certo, #bigdaddy?
-Obrigada, anjo... Ei, #bigdaddy, você acha que anjos realmente existem? Se de fato existissem anjos, quão maravilhoso seria.</t>
+          <t>...Hehe, um novo Pequenino veio para nós, #bigdaddy. Não está mais perdido. De agora em diante, vamos protegê-la, custe o que custar... né, #bigdaddy?
+Obrigada, anjo...Ei, #bigdaddy, você acha que anjos existem de verdade? Se realmente houvesse anjos, que maravilha seria.</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>... Nosso pequeno... Nosso Pequeno... Os anjos são cruéis, #bigdaddy... Os anjos deixam nosso pequeno morrer. Devemos... Protegê-los... Deste vasto mundo. Aqui... para eles... o Pequeno... Jardim…</t>
+          <t>...Nosso Pequenino... nosso Pequeninho... Os anjos são cruéis, #bigdaddy...Os anjos deixaram o nosso Pequenino morrer. Temos...de protegê-los...deste mundo vasto. Aqui..para eles... o Pequeno..Jardim...</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Ahaha, não há anjos. Mas está tudo bem, desde que o #bigdaddy esteja aqui.</t>
+          <t>Ahaha, não existem anjos. Mas tá tudo bem, contanto que o #bigdaddy esteja aqui.</t>
         </is>
       </c>
     </row>
